--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -816,22 +816,22 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -848,22 +848,22 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1606,19 +1606,19 @@
         <v>48</v>
       </c>
       <c r="D31">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>74.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H31" s="1">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="I31" s="2">
         <v>5.7</v>
@@ -1641,19 +1641,19 @@
         <v>49</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32">
         <v>19</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
       <c r="H32" s="1">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="I32" s="2">
         <v>5.5</v>
@@ -1676,28 +1676,28 @@
         <v>50</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>14</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H33" s="1">
-        <v>22.2</v>
+        <v>26.3</v>
       </c>
       <c r="I33" s="2">
         <v>6.4</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1708,28 +1708,28 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34">
         <v>49</v>
       </c>
       <c r="G34" s="1">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="H34" s="1">
-        <v>36.8</v>
+        <v>37.1</v>
       </c>
       <c r="I34" s="2">
         <v>5.9</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1743,22 +1743,22 @@
         <v>51</v>
       </c>
       <c r="D35">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35">
         <v>36</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H35" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1775,22 +1775,22 @@
         <v>22</v>
       </c>
       <c r="D36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>36</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H36" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2046,28 +2046,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E44">
         <v>783</v>
       </c>
       <c r="F44">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G44" s="1">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="H44" s="1">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="I44" s="2">
         <v>6.8</v>
       </c>
       <c r="J44">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K44" s="1">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -2339,13 +2339,13 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -2371,13 +2371,13 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -3129,13 +3129,13 @@
         <v>48</v>
       </c>
       <c r="D31">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -3164,13 +3164,13 @@
         <v>49</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -3199,13 +3199,13 @@
         <v>50</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -3231,13 +3231,13 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -3266,13 +3266,13 @@
         <v>51</v>
       </c>
       <c r="D35">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -3298,13 +3298,13 @@
         <v>22</v>
       </c>
       <c r="D36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -3569,13 +3569,13 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -3862,22 +3862,22 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3894,22 +3894,22 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4652,19 +4652,19 @@
         <v>48</v>
       </c>
       <c r="D31">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>74.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H31" s="1">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="I31" s="2">
         <v>5.7</v>
@@ -4687,19 +4687,19 @@
         <v>49</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32">
         <v>19</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
       <c r="H32" s="1">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="I32" s="2">
         <v>5.5</v>
@@ -4722,28 +4722,28 @@
         <v>50</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>14</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H33" s="1">
-        <v>22.2</v>
+        <v>26.3</v>
       </c>
       <c r="I33" s="2">
         <v>6.4</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4754,28 +4754,28 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34">
         <v>49</v>
       </c>
       <c r="G34" s="1">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="H34" s="1">
-        <v>36.8</v>
+        <v>37.1</v>
       </c>
       <c r="I34" s="2">
         <v>5.9</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4789,22 +4789,22 @@
         <v>51</v>
       </c>
       <c r="D35">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35">
         <v>36</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H35" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4821,22 +4821,22 @@
         <v>22</v>
       </c>
       <c r="D36">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>36</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H36" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5092,28 +5092,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E44">
         <v>783</v>
       </c>
       <c r="F44">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G44" s="1">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="H44" s="1">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="I44" s="2">
         <v>6.8</v>
       </c>
       <c r="J44">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K44" s="1">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -749,28 +749,28 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H6" s="1">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I6" s="2">
         <v>6.3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -781,28 +781,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7">
         <v>72</v>
       </c>
       <c r="F7">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7" s="1">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="H7" s="1">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="I7" s="2">
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1297,28 +1297,28 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22">
         <v>28</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>84.8</v>
+        <v>90.3</v>
       </c>
       <c r="H22" s="1">
-        <v>15.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I22" s="2">
         <v>7.4</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1364,28 +1364,28 @@
         <v>22</v>
       </c>
       <c r="D24">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E24">
         <v>107</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>16.4</v>
+        <v>15.1</v>
       </c>
       <c r="I24" s="2">
         <v>7.4</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2046,28 +2046,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E44">
         <v>783</v>
       </c>
       <c r="F44">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G44" s="1">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="H44" s="1">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I44" s="2">
         <v>6.8</v>
       </c>
       <c r="J44">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K44" s="1">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -2272,13 +2272,13 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -2304,13 +2304,13 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -2820,13 +2820,13 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -2887,13 +2887,13 @@
         <v>22</v>
       </c>
       <c r="D24">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -3569,13 +3569,13 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="K44" s="1">
         <v>100</v>
@@ -3795,28 +3795,28 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H6" s="1">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="I6" s="2">
         <v>6.3</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3827,28 +3827,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7">
         <v>72</v>
       </c>
       <c r="F7">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7" s="1">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="H7" s="1">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="I7" s="2">
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4343,28 +4343,28 @@
         <v>41</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22">
         <v>28</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>84.8</v>
+        <v>90.3</v>
       </c>
       <c r="H22" s="1">
-        <v>15.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I22" s="2">
         <v>7.4</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4410,28 +4410,28 @@
         <v>22</v>
       </c>
       <c r="D24">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E24">
         <v>107</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>16.4</v>
+        <v>15.1</v>
       </c>
       <c r="I24" s="2">
         <v>7.1</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -5092,28 +5092,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E44">
         <v>783</v>
       </c>
       <c r="F44">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G44" s="1">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="H44" s="1">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="I44" s="2">
         <v>6.8</v>
       </c>
       <c r="J44">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K44" s="1">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -816,22 +816,22 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H8" s="1">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -848,22 +848,22 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H9" s="1">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1058,22 +1058,22 @@
         <v>36</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1125,19 +1125,19 @@
         <v>22</v>
       </c>
       <c r="D17">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E17">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F17">
         <v>46</v>
       </c>
       <c r="G17" s="1">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H17" s="1">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="I17" s="2">
         <v>6.7</v>
@@ -1163,25 +1163,25 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1195,25 +1195,25 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1230,25 +1230,25 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="H20" s="1">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2">
         <v>6.5</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1367,25 +1367,25 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1">
-        <v>84.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H24" s="1">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="I24" s="2">
         <v>7.4</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1399,19 +1399,19 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25">
         <v>8</v>
       </c>
       <c r="G25" s="1">
-        <v>78.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="H25" s="1">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="I25" s="2">
         <v>7</v>
@@ -1536,19 +1536,19 @@
         <v>22</v>
       </c>
       <c r="D29">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F29">
         <v>17</v>
       </c>
       <c r="G29" s="1">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="H29" s="1">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="I29" s="2">
         <v>7.7</v>
@@ -1606,19 +1606,19 @@
         <v>48</v>
       </c>
       <c r="D31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="I31" s="2">
         <v>5.7</v>
@@ -1708,19 +1708,19 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F34">
         <v>49</v>
       </c>
       <c r="G34" s="1">
-        <v>62.9</v>
+        <v>63.2</v>
       </c>
       <c r="H34" s="1">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="I34" s="2">
         <v>5.9</v>
@@ -1985,22 +1985,22 @@
         <v>57</v>
       </c>
       <c r="D42">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F42">
         <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>82.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H42" s="1">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="I42" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2017,10 +2017,10 @@
         <v>22</v>
       </c>
       <c r="D43">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43">
         <v>24</v>
@@ -2046,28 +2046,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E44">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="F44">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="G44" s="1">
-        <v>76.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>23.7</v>
+        <v>21.1</v>
       </c>
       <c r="I44" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J44">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2135,25 +2135,25 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2170,25 +2170,25 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>48.5</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2205,25 +2205,25 @@
         <v>16</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2240,25 +2240,25 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>11.5</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2275,25 +2275,25 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2307,25 +2307,25 @@
         <v>124</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F7">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>38.7</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2339,13 +2339,13 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -2371,13 +2371,13 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -2409,25 +2409,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2444,25 +2444,25 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2479,25 +2479,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2514,25 +2514,25 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>18.2</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2549,25 +2549,25 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2581,28 +2581,28 @@
         <v>36</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2619,25 +2619,25 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2648,28 +2648,28 @@
         <v>22</v>
       </c>
       <c r="D17">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F17">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2753,25 +2753,25 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2788,25 +2788,25 @@
         <v>38</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F21">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J21">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2858,25 +2858,25 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>25.9</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J23">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2890,25 +2890,25 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F24">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>63.5</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>36.5</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J24">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2922,28 +2922,28 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J25">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2960,25 +2960,25 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J26">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2995,25 +2995,25 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>15.4</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3030,25 +3030,25 @@
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3059,28 +3059,28 @@
         <v>22</v>
       </c>
       <c r="D29">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F29">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J29">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3129,13 +3129,13 @@
         <v>48</v>
       </c>
       <c r="D31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -3231,13 +3231,13 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -3269,25 +3269,25 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F35">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3301,25 +3301,25 @@
         <v>40</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F36">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J36">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3508,28 +3508,28 @@
         <v>57</v>
       </c>
       <c r="D42">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F42">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H42" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3540,28 +3540,28 @@
         <v>22</v>
       </c>
       <c r="D43">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F43">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="H43" s="1">
-        <v>100</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J43">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3569,28 +3569,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="F44">
-        <v>1026</v>
+        <v>489</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="H44" s="1">
-        <v>100</v>
+        <v>47.6</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J44">
-        <v>1026</v>
+        <v>371</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>36.1</v>
       </c>
     </row>
   </sheetData>
@@ -3658,19 +3658,19 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1">
-        <v>45.9</v>
+        <v>40.5</v>
       </c>
       <c r="H2" s="1">
-        <v>54.1</v>
+        <v>59.5</v>
       </c>
       <c r="I2" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3693,19 +3693,19 @@
         <v>33</v>
       </c>
       <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
         <v>16</v>
       </c>
-      <c r="F3">
-        <v>17</v>
-      </c>
       <c r="G3" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="H3" s="1">
         <v>48.5</v>
       </c>
-      <c r="H3" s="1">
-        <v>51.5</v>
-      </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3728,19 +3728,19 @@
         <v>16</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="H4" s="1">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>11.5</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3798,19 +3798,19 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H6" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3830,19 +3830,19 @@
         <v>124</v>
       </c>
       <c r="E7">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F7">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="H7" s="1">
-        <v>41.9</v>
+        <v>38.7</v>
       </c>
       <c r="I7" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3862,22 +3862,22 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H8" s="1">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3894,22 +3894,22 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H9" s="1">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3932,19 +3932,19 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>75.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3967,19 +3967,19 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>92.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H11" s="1">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4002,19 +4002,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>80.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>19.4</v>
+        <v>5.6</v>
       </c>
       <c r="I12" s="2">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4037,19 +4037,19 @@
         <v>44</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>79.5</v>
+        <v>81.8</v>
       </c>
       <c r="H13" s="1">
-        <v>20.5</v>
+        <v>18.2</v>
       </c>
       <c r="I13" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4072,19 +4072,19 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>78.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>6.2</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4104,22 +4104,22 @@
         <v>36</v>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4142,19 +4142,19 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="H16" s="1">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="I16" s="2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4171,22 +4171,22 @@
         <v>22</v>
       </c>
       <c r="D17">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E17">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F17">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G17" s="1">
-        <v>81.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>18.9</v>
+        <v>11.4</v>
       </c>
       <c r="I17" s="2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4209,25 +4209,25 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4241,25 +4241,25 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4276,25 +4276,25 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="H20" s="1">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4323,7 +4323,7 @@
         <v>5.3</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4413,25 +4413,25 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1">
-        <v>84.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H24" s="1">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="I24" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4445,22 +4445,22 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="1">
-        <v>78.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H25" s="1">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="I25" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4483,19 +4483,19 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1">
-        <v>79.2</v>
+        <v>83.3</v>
       </c>
       <c r="H26" s="1">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>15.4</v>
       </c>
       <c r="I27" s="2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4582,22 +4582,22 @@
         <v>22</v>
       </c>
       <c r="D29">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F29">
         <v>17</v>
       </c>
       <c r="G29" s="1">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="H29" s="1">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="I29" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4652,19 +4652,19 @@
         <v>48</v>
       </c>
       <c r="D31">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="I31" s="2">
         <v>5.7</v>
@@ -4754,19 +4754,19 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F34">
         <v>49</v>
       </c>
       <c r="G34" s="1">
-        <v>62.9</v>
+        <v>63.2</v>
       </c>
       <c r="H34" s="1">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="I34" s="2">
         <v>5.9</v>
@@ -4804,7 +4804,7 @@
         <v>10</v>
       </c>
       <c r="I35" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5031,22 +5031,22 @@
         <v>57</v>
       </c>
       <c r="D42">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F42">
         <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>82.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H42" s="1">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="I42" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>22</v>
       </c>
       <c r="D43">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43">
         <v>24</v>
@@ -5078,7 +5078,7 @@
         <v>13.3</v>
       </c>
       <c r="I43" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5092,28 +5092,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E44">
-        <v>783</v>
+        <v>832</v>
       </c>
       <c r="F44">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="G44" s="1">
-        <v>76.3</v>
+        <v>81</v>
       </c>
       <c r="H44" s="1">
-        <v>23.7</v>
+        <v>19</v>
       </c>
       <c r="I44" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J44">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -1694,10 +1694,10 @@
         <v>6.4</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1726,10 +1726,10 @@
         <v>5.9</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2064,10 +2064,10 @@
         <v>7.1</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2686,25 +2686,25 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2718,25 +2718,25 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2823,25 +2823,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2890,25 +2890,25 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="F24">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1">
-        <v>63.5</v>
+        <v>86.5</v>
       </c>
       <c r="H24" s="1">
-        <v>36.5</v>
+        <v>13.5</v>
       </c>
       <c r="I24" s="2">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>24.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3097,25 +3097,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>52.8</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3132,25 +3132,25 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>51.3</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>48.7</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J31">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3167,25 +3167,25 @@
         <v>39</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J32">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3202,25 +3202,25 @@
         <v>19</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J33">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3234,25 +3234,25 @@
         <v>133</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F34">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J34">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3336,25 +3336,25 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J37">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3371,25 +3371,25 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F38">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J38">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3476,25 +3476,25 @@
         <v>25</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3543,25 +3543,25 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F43">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="G43" s="1">
-        <v>16.6</v>
+        <v>48.1</v>
       </c>
       <c r="H43" s="1">
-        <v>83.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="I43" s="2">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J43">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="K43" s="1">
-        <v>80.09999999999999</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3572,25 +3572,25 @@
         <v>1027</v>
       </c>
       <c r="E44">
-        <v>538</v>
+        <v>708</v>
       </c>
       <c r="F44">
-        <v>489</v>
+        <v>319</v>
       </c>
       <c r="G44" s="1">
-        <v>52.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>47.6</v>
+        <v>31.1</v>
       </c>
       <c r="I44" s="2">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="J44">
-        <v>371</v>
+        <v>103</v>
       </c>
       <c r="K44" s="1">
-        <v>36.1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4221,7 +4221,7 @@
         <v>10.7</v>
       </c>
       <c r="I18" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>10.7</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4346,19 +4346,19 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>90.3</v>
+        <v>93.5</v>
       </c>
       <c r="H22" s="1">
-        <v>9.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4413,19 +4413,19 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F24">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1">
-        <v>85.7</v>
+        <v>86.5</v>
       </c>
       <c r="H24" s="1">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="I24" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4620,19 +4620,19 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G30" s="1">
-        <v>61.1</v>
+        <v>47.2</v>
       </c>
       <c r="H30" s="1">
-        <v>38.9</v>
+        <v>52.8</v>
       </c>
       <c r="I30" s="2">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4655,19 +4655,19 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1">
-        <v>74.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="H31" s="1">
-        <v>25.6</v>
+        <v>48.7</v>
       </c>
       <c r="I31" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4690,19 +4690,19 @@
         <v>39</v>
       </c>
       <c r="E32">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G32" s="1">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="H32" s="1">
-        <v>51.3</v>
+        <v>66.7</v>
       </c>
       <c r="I32" s="2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4725,25 +4725,25 @@
         <v>19</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>73.7</v>
+        <v>47.4</v>
       </c>
       <c r="H33" s="1">
-        <v>26.3</v>
+        <v>52.6</v>
       </c>
       <c r="I33" s="2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4757,25 +4757,25 @@
         <v>133</v>
       </c>
       <c r="E34">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F34">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="G34" s="1">
-        <v>63.2</v>
+        <v>44.4</v>
       </c>
       <c r="H34" s="1">
-        <v>36.8</v>
+        <v>55.6</v>
       </c>
       <c r="I34" s="2">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4859,19 +4859,19 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G37" s="1">
-        <v>81.5</v>
+        <v>66.7</v>
       </c>
       <c r="H37" s="1">
-        <v>18.5</v>
+        <v>33.3</v>
       </c>
       <c r="I37" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4894,19 +4894,19 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H38" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I38" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4999,19 +4999,19 @@
         <v>25</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H41" s="1">
+        <v>16</v>
+      </c>
+      <c r="I41" s="2">
         <v>8</v>
-      </c>
-      <c r="I41" s="2">
-        <v>7.8</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -5066,16 +5066,16 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F43">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G43" s="1">
-        <v>86.7</v>
+        <v>82.3</v>
       </c>
       <c r="H43" s="1">
-        <v>13.3</v>
+        <v>17.7</v>
       </c>
       <c r="I43" s="2">
         <v>7.7</v>
@@ -5095,25 +5095,25 @@
         <v>1027</v>
       </c>
       <c r="E44">
-        <v>832</v>
+        <v>800</v>
       </c>
       <c r="F44">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G44" s="1">
-        <v>81</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>19</v>
+        <v>22.1</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -2342,25 +2342,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2374,25 +2374,25 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3406,25 +3406,25 @@
         <v>39</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F39">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3441,25 +3441,25 @@
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F40">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>13.3</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J40">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3543,25 +3543,25 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="F43">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="G43" s="1">
-        <v>48.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H43" s="1">
-        <v>51.9</v>
+        <v>17.1</v>
       </c>
       <c r="I43" s="2">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="J43">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3572,25 +3572,25 @@
         <v>1027</v>
       </c>
       <c r="E44">
-        <v>708</v>
+        <v>802</v>
       </c>
       <c r="F44">
-        <v>319</v>
+        <v>225</v>
       </c>
       <c r="G44" s="1">
-        <v>68.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H44" s="1">
-        <v>31.1</v>
+        <v>21.9</v>
       </c>
       <c r="I44" s="2">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="J44">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3865,19 +3865,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H8" s="1">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3897,19 +3897,19 @@
         <v>34</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H9" s="1">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4964,19 +4964,19 @@
         <v>30</v>
       </c>
       <c r="E40">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G40" s="1">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="H40" s="1">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="I40" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -5066,16 +5066,16 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G43" s="1">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H43" s="1">
-        <v>17.7</v>
+        <v>17.1</v>
       </c>
       <c r="I43" s="2">
         <v>7.7</v>
@@ -5095,16 +5095,16 @@
         <v>1027</v>
       </c>
       <c r="E44">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F44">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G44" s="1">
-        <v>77.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H44" s="1">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -749,28 +749,28 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="H6" s="1">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I6" s="2">
         <v>6.3</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -781,28 +781,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7">
         <v>72</v>
       </c>
       <c r="F7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" s="1">
-        <v>58.1</v>
+        <v>57.6</v>
       </c>
       <c r="H7" s="1">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="I7" s="2">
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1230,16 +1230,16 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
         <v>6.5</v>
@@ -1265,19 +1265,19 @@
         <v>38</v>
       </c>
       <c r="E21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1335,19 +1335,19 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>74.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>25.9</v>
+        <v>7.4</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1367,19 +1367,19 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F24">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>85.7</v>
+        <v>96</v>
       </c>
       <c r="H24" s="1">
-        <v>14.3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         <v>36</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H42" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F43">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G43" s="1">
-        <v>86.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H43" s="1">
-        <v>13.3</v>
+        <v>9.9</v>
       </c>
       <c r="I43" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2046,28 +2046,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E44">
-        <v>810</v>
+        <v>829</v>
       </c>
       <c r="F44">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="G44" s="1">
-        <v>78.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H44" s="1">
-        <v>21.1</v>
+        <v>19.4</v>
       </c>
       <c r="I44" s="2">
         <v>7.1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2272,28 +2272,28 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="H6" s="1">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="I6" s="2">
         <v>7.4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2304,28 +2304,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7">
         <v>76</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
       <c r="H7" s="1">
-        <v>38.7</v>
+        <v>39.2</v>
       </c>
       <c r="I7" s="2">
         <v>7.1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2753,16 +2753,16 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
         <v>6.7</v>
@@ -2788,16 +2788,16 @@
         <v>38</v>
       </c>
       <c r="E21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
         <v>8.300000000000001</v>
@@ -2858,16 +2858,16 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>74.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>25.9</v>
+        <v>7.4</v>
       </c>
       <c r="I23" s="2">
         <v>6.6</v>
@@ -2890,16 +2890,16 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F24">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="H24" s="1">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I24" s="2">
         <v>7.4</v>
@@ -3511,16 +3511,16 @@
         <v>36</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H42" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
         <v>7</v>
@@ -3543,16 +3543,16 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F43">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G43" s="1">
-        <v>82.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H43" s="1">
-        <v>17.1</v>
+        <v>13.8</v>
       </c>
       <c r="I43" s="2">
         <v>7.6</v>
@@ -3569,28 +3569,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E44">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="F44">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="G44" s="1">
-        <v>78.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>21.9</v>
+        <v>20.1</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3795,28 +3795,28 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="H6" s="1">
-        <v>25</v>
+        <v>30.8</v>
       </c>
       <c r="I6" s="2">
         <v>7</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3827,28 +3827,28 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7">
         <v>76</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
       <c r="H7" s="1">
-        <v>38.7</v>
+        <v>39.2</v>
       </c>
       <c r="I7" s="2">
         <v>6.8</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4276,19 +4276,19 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4311,19 +4311,19 @@
         <v>38</v>
       </c>
       <c r="E21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4381,19 +4381,19 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="1">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="H23" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="I23" s="2">
         <v>7</v>
-      </c>
-      <c r="G23" s="1">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="H23" s="1">
-        <v>25.9</v>
-      </c>
-      <c r="I23" s="2">
-        <v>6.7</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4413,19 +4413,19 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F24">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="H24" s="1">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -5034,19 +5034,19 @@
         <v>36</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H42" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F43">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G43" s="1">
-        <v>82.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H43" s="1">
-        <v>17.1</v>
+        <v>13.8</v>
       </c>
       <c r="I43" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5092,28 +5092,28 @@
         <v>24</v>
       </c>
       <c r="D44">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E44">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="F44">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="G44" s="1">
-        <v>78.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>21.9</v>
+        <v>20.1</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -764,13 +764,13 @@
         <v>53.8</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -799,10 +799,10 @@
         <v>6.4</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2064,10 +2064,10 @@
         <v>7.1</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2287,13 +2287,13 @@
         <v>30.8</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2319,13 +2319,13 @@
         <v>39.2</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2619,19 +2619,19 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="H16" s="1">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="I16" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2651,16 +2651,16 @@
         <v>245</v>
       </c>
       <c r="E17">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="1">
-        <v>88.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="H17" s="1">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="I17" s="2">
         <v>7.9</v>
@@ -3572,25 +3572,25 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F44">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G44" s="1">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H44" s="1">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="I44" s="2">
         <v>7.3</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3658,19 +3658,19 @@
         <v>37</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>40.5</v>
+        <v>51.4</v>
       </c>
       <c r="H2" s="1">
-        <v>59.5</v>
+        <v>48.6</v>
       </c>
       <c r="I2" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3693,19 +3693,19 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>51.5</v>
+        <v>84.8</v>
       </c>
       <c r="H3" s="1">
-        <v>48.5</v>
+        <v>15.2</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3728,19 +3728,19 @@
         <v>16</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H4" s="1">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3763,16 +3763,16 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>88.5</v>
+        <v>96.2</v>
       </c>
       <c r="H5" s="1">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="I5" s="2">
         <v>7.5</v>
@@ -3798,25 +3798,25 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3830,25 +3830,25 @@
         <v>125</v>
       </c>
       <c r="E7">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F7">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G7" s="1">
-        <v>60.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>39.2</v>
+        <v>22.4</v>
       </c>
       <c r="I7" s="2">
         <v>6.8</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3877,7 +3877,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3967,19 +3967,19 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>90.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4002,19 +4002,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>94.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H12" s="1">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>18.2</v>
       </c>
       <c r="I13" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4142,19 +4142,19 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4174,19 +4174,19 @@
         <v>245</v>
       </c>
       <c r="E17">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F17">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1">
-        <v>88.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="H17" s="1">
-        <v>11.4</v>
+        <v>6.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4346,16 +4346,16 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>7.9</v>
@@ -4381,16 +4381,16 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>92.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H23" s="1">
-        <v>7.4</v>
+        <v>14.8</v>
       </c>
       <c r="I23" s="2">
         <v>7</v>
@@ -4448,16 +4448,16 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="I25" s="2">
         <v>6.9</v>
@@ -4483,16 +4483,16 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H26" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="2">
         <v>7.8</v>
@@ -4518,19 +4518,19 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>84.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="H27" s="1">
-        <v>15.4</v>
+        <v>11.5</v>
       </c>
       <c r="I27" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4585,19 +4585,19 @@
         <v>116</v>
       </c>
       <c r="E29">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F29">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1">
-        <v>85.3</v>
+        <v>88.8</v>
       </c>
       <c r="H29" s="1">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4792,19 +4792,19 @@
         <v>40</v>
       </c>
       <c r="E35">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="H35" s="1">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I35" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4824,19 +4824,19 @@
         <v>40</v>
       </c>
       <c r="E36">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" s="1">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="H36" s="1">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I36" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4859,19 +4859,19 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>66.7</v>
+        <v>85.2</v>
       </c>
       <c r="H37" s="1">
-        <v>33.3</v>
+        <v>14.8</v>
       </c>
       <c r="I37" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4894,16 +4894,16 @@
         <v>24</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="H38" s="1">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="I38" s="2">
         <v>7.5</v>
@@ -4929,19 +4929,19 @@
         <v>39</v>
       </c>
       <c r="E39">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="1">
-        <v>94.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H39" s="1">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="I39" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4964,19 +4964,19 @@
         <v>30</v>
       </c>
       <c r="E40">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1">
-        <v>86.7</v>
+        <v>96.7</v>
       </c>
       <c r="H40" s="1">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="I40" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4999,16 +4999,16 @@
         <v>25</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>96</v>
+      </c>
+      <c r="H41" s="1">
         <v>4</v>
-      </c>
-      <c r="G41" s="1">
-        <v>84</v>
-      </c>
-      <c r="H41" s="1">
-        <v>16</v>
       </c>
       <c r="I41" s="2">
         <v>8</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>181</v>
       </c>
       <c r="E43">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G43" s="1">
-        <v>86.2</v>
+        <v>92.8</v>
       </c>
       <c r="H43" s="1">
-        <v>13.8</v>
+        <v>7.2</v>
       </c>
       <c r="I43" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5095,25 +5095,25 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>821</v>
+        <v>871</v>
       </c>
       <c r="F44">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="G44" s="1">
-        <v>79.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="H44" s="1">
-        <v>20.1</v>
+        <v>15.3</v>
       </c>
       <c r="I44" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -4209,16 +4209,16 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>89.3</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>7.4</v>
@@ -4241,16 +4241,16 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>89.3</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>7.4</v>
@@ -4725,19 +4725,19 @@
         <v>19</v>
       </c>
       <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
         <v>9</v>
       </c>
-      <c r="F33">
-        <v>10</v>
-      </c>
       <c r="G33" s="1">
+        <v>52.6</v>
+      </c>
+      <c r="H33" s="1">
         <v>47.4</v>
       </c>
-      <c r="H33" s="1">
-        <v>52.6</v>
-      </c>
       <c r="I33" s="2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4757,16 +4757,16 @@
         <v>133</v>
       </c>
       <c r="E34">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F34">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G34" s="1">
-        <v>44.4</v>
+        <v>45.1</v>
       </c>
       <c r="H34" s="1">
-        <v>55.6</v>
+        <v>54.9</v>
       </c>
       <c r="I34" s="2">
         <v>5.6</v>
@@ -5095,16 +5095,16 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="F44">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G44" s="1">
-        <v>84.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H44" s="1">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="I44" s="2">
         <v>7.2</v>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -1472,19 +1472,19 @@
         <v>26</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1">
-        <v>84.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="H27" s="1">
-        <v>15.4</v>
+        <v>11.5</v>
       </c>
       <c r="I27" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1539,19 +1539,19 @@
         <v>116</v>
       </c>
       <c r="E29">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G29" s="1">
-        <v>85.3</v>
+        <v>86.2</v>
       </c>
       <c r="H29" s="1">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
       <c r="I29" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2049,16 +2049,16 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F44">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G44" s="1">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="H44" s="1">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I44" s="2">
         <v>7.1</v>
@@ -4448,16 +4448,16 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H25" s="1">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="I25" s="2">
         <v>6.9</v>
@@ -4530,7 +4530,7 @@
         <v>11.5</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4585,19 +4585,19 @@
         <v>116</v>
       </c>
       <c r="E29">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" s="1">
-        <v>88.8</v>
+        <v>89.7</v>
       </c>
       <c r="H29" s="1">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="I29" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4620,19 +4620,19 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" s="1">
-        <v>47.2</v>
+        <v>44.4</v>
       </c>
       <c r="H30" s="1">
-        <v>52.8</v>
+        <v>55.6</v>
       </c>
       <c r="I30" s="2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4690,19 +4690,19 @@
         <v>39</v>
       </c>
       <c r="E32">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G32" s="1">
-        <v>33.3</v>
+        <v>53.8</v>
       </c>
       <c r="H32" s="1">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="I32" s="2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4757,16 +4757,16 @@
         <v>133</v>
       </c>
       <c r="E34">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F34">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G34" s="1">
-        <v>45.1</v>
+        <v>50.4</v>
       </c>
       <c r="H34" s="1">
-        <v>54.9</v>
+        <v>49.6</v>
       </c>
       <c r="I34" s="2">
         <v>5.6</v>
@@ -5095,16 +5095,16 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="F44">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G44" s="1">
-        <v>85.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="I44" s="2">
         <v>7.2</v>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -4655,16 +4655,16 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G31" s="1">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="H31" s="1">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="I31" s="2">
         <v>5.6</v>
@@ -4757,16 +4757,16 @@
         <v>133</v>
       </c>
       <c r="E34">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F34">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G34" s="1">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="H34" s="1">
-        <v>49.6</v>
+        <v>48.9</v>
       </c>
       <c r="I34" s="2">
         <v>5.6</v>
@@ -5095,16 +5095,16 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F44">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G44" s="1">
-        <v>85.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H44" s="1">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="I44" s="2">
         <v>7.2</v>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -3670,7 +3670,7 @@
         <v>48.6</v>
       </c>
       <c r="I2" s="2">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>15.2</v>
       </c>
       <c r="I3" s="2">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>3.8</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3810,7 +3810,7 @@
         <v>15.4</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>22.4</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>18.2</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4186,7 +4186,7 @@
         <v>6.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>14.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         <v>3.2</v>
       </c>
       <c r="I24" s="2">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>16.7</v>
       </c>
       <c r="I25" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4495,7 +4495,7 @@
         <v>12.5</v>
       </c>
       <c r="I26" s="2">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>11.5</v>
       </c>
       <c r="I27" s="2">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4597,7 +4597,7 @@
         <v>10.3</v>
       </c>
       <c r="I29" s="2">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>55.6</v>
       </c>
       <c r="I30" s="2">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>46.2</v>
       </c>
       <c r="I31" s="2">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4702,7 +4702,7 @@
         <v>46.2</v>
       </c>
       <c r="I32" s="2">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4737,7 +4737,7 @@
         <v>47.4</v>
       </c>
       <c r="I33" s="2">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>48.9</v>
       </c>
       <c r="I34" s="2">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4804,7 +4804,7 @@
         <v>7.5</v>
       </c>
       <c r="I35" s="2">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>7.5</v>
       </c>
       <c r="I36" s="2">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4871,7 +4871,7 @@
         <v>14.8</v>
       </c>
       <c r="I37" s="2">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>16.7</v>
       </c>
       <c r="I38" s="2">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4941,7 +4941,7 @@
         <v>7.7</v>
       </c>
       <c r="I39" s="2">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         <v>3.3</v>
       </c>
       <c r="I40" s="2">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -5011,7 +5011,7 @@
         <v>4</v>
       </c>
       <c r="I41" s="2">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>7.2</v>
       </c>
       <c r="I43" s="2">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5107,7 +5107,7 @@
         <v>14</v>
       </c>
       <c r="I44" s="2">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J44">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20231.xlsx
+++ b/academias/Matemáticas - Estadisticos 20231.xlsx
@@ -3670,7 +3670,7 @@
         <v>48.6</v>
       </c>
       <c r="I2" s="2">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>15.2</v>
       </c>
       <c r="I3" s="2">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>3.8</v>
       </c>
       <c r="I5" s="2">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3810,7 +3810,7 @@
         <v>15.4</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>22.4</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I8" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I12" s="2">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>18.2</v>
       </c>
       <c r="I13" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>6.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4186,7 +4186,7 @@
         <v>6.5</v>
       </c>
       <c r="I17" s="2">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4381,19 +4381,19 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="1">
-        <v>85.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="I23" s="2">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4413,19 +4413,19 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" s="1">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I24" s="2">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>16.7</v>
       </c>
       <c r="I25" s="2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4495,7 +4495,7 @@
         <v>12.5</v>
       </c>
       <c r="I26" s="2">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>11.5</v>
       </c>
       <c r="I27" s="2">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4597,7 +4597,7 @@
         <v>10.3</v>
       </c>
       <c r="I29" s="2">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>55.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>46.2</v>
       </c>
       <c r="I31" s="2">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4702,7 +4702,7 @@
         <v>46.2</v>
       </c>
       <c r="I32" s="2">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4737,7 +4737,7 @@
         <v>47.4</v>
       </c>
       <c r="I33" s="2">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>48.9</v>
       </c>
       <c r="I34" s="2">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4804,7 +4804,7 @@
         <v>7.5</v>
       </c>
       <c r="I35" s="2">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>7.5</v>
       </c>
       <c r="I36" s="2">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4871,7 +4871,7 @@
         <v>14.8</v>
       </c>
       <c r="I37" s="2">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>16.7</v>
       </c>
       <c r="I38" s="2">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4941,7 +4941,7 @@
         <v>7.7</v>
       </c>
       <c r="I39" s="2">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         <v>3.3</v>
       </c>
       <c r="I40" s="2">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -5011,7 +5011,7 @@
         <v>4</v>
       </c>
       <c r="I41" s="2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>7.2</v>
       </c>
       <c r="I43" s="2">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5095,19 +5095,19 @@
         <v>1028</v>
       </c>
       <c r="E44">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F44">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G44" s="1">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H44" s="1">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="I44" s="2">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J44">
         <v>0</v>
